--- a/artfynd/A 23965-2026 artfynd.xlsx
+++ b/artfynd/A 23965-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>159986</v>
+        <v>159985</v>
       </c>
       <c r="B2" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495914.4652705074</v>
+        <v>495925</v>
       </c>
       <c r="R2" t="n">
-        <v>6473839.278823275</v>
+        <v>6473760</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1997-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6740690</v>
+        <v>159986</v>
       </c>
       <c r="B3" t="n">
-        <v>77955</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>374</v>
+        <v>311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495864.6131837316</v>
+        <v>495914</v>
       </c>
       <c r="R3" t="n">
-        <v>6473858.719079191</v>
+        <v>6473839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>1997-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>159985</v>
+        <v>206460</v>
       </c>
       <c r="B4" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>STAVLÖSA LÖVSKOG, Ög</t>
+          <t>(08E5j03), Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495925.4071577943</v>
+        <v>495914</v>
       </c>
       <c r="R4" t="n">
-        <v>6473759.617941666</v>
+        <v>6473813</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-11-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>080459031 / CHA PHAE / Enstaka-sparsam (1)  / OBJ.AREA:0,7 ha</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,38 +978,37 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Tingvall</t>
+          <t>Ulf Kleist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>357914</v>
+        <v>6740690</v>
       </c>
       <c r="B5" t="n">
-        <v>78007</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1348</v>
+        <v>374</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hjälmbrosklav</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramalina baltica</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lettau</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495864.6131837316</v>
+        <v>495865</v>
       </c>
       <c r="R5" t="n">
-        <v>6473858.719079191</v>
+        <v>6473859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1073,9 @@
           <t>1997-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,15 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>357913</v>
+        <v>182574</v>
       </c>
       <c r="B6" t="n">
-        <v>78007</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1348</v>
+        <v>1114</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hjälmbrosklav</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramalina baltica</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lettau</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495834.6787370465</v>
+        <v>495925</v>
       </c>
       <c r="R6" t="n">
-        <v>6473848.270626385</v>
+        <v>6473760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,24 +1180,9 @@
           <t>1997-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikt med Calicium viride och busklavar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,15 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>190084</v>
+        <v>182575</v>
       </c>
       <c r="B7" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,17 +1250,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>(08E5j03), Ög</t>
+          <t>STAVLÖSA LÖVSKOG, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495913.9125187675</v>
+        <v>495914</v>
       </c>
       <c r="R7" t="n">
-        <v>6473812.555065274</v>
+        <v>6473839</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,27 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1998-11-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1998-11-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>080459031 / BUE VIOL / Enstaka-sparsam (1)  / OBJ.AREA:0,7 ha</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,42 +1303,33 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Grova ädellövträd /</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Gammal grov ek</t>
-        </is>
-      </c>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Tommy Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Kleist</t>
+          <t>Anders Tingvall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+          <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>182574</v>
+        <v>190084</v>
       </c>
       <c r="B8" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,17 +1357,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>STAVLÖSA LÖVSKOG, Ög</t>
+          <t>(08E5j03), Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495925.4071577943</v>
+        <v>495914</v>
       </c>
       <c r="R8" t="n">
-        <v>6473759.617941666</v>
+        <v>6473813</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1491,22 +1391,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-11-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>080459031 / BUE VIOL / Enstaka-sparsam (1)  / OBJ.AREA:0,7 ha</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,38 +1415,37 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Tingvall</t>
+          <t>Ulf Kleist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>182575</v>
+        <v>357913</v>
       </c>
       <c r="B9" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1114</v>
+        <v>1348</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Hjälmbrosklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Ramalina baltica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>Lettau</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1583,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495914.4652705074</v>
+        <v>495835</v>
       </c>
       <c r="R9" t="n">
-        <v>6473839.278823275</v>
+        <v>6473848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,19 +1510,14 @@
           <t>1997-01-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1998-01-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikt med Calicium viride och busklavar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,6 +1547,113 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Sällsynta lavar i Östergötland 2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>357914</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79847</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1348</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Hjälmbrosklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramalina baltica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Lettau</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>STAVLÖSA LÖVSKOG, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>495865</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6473859</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vadstena</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hov</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Tingvall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>

--- a/artfynd/A 23965-2026 artfynd.xlsx
+++ b/artfynd/A 23965-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/159985</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/159986</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/206460</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6740690</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/182574</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/182575</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/190084</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/357913</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,8 +1703,24 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/357914</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>